--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/08 12:06:24</t>
+          <t>09/15 10:26:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/08 15:08:10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>20000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>20000</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/15 11:36:58</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>170000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>170000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20000</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15 10:26:14</t>
+          <t>09/17 10:03:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>毕春丽</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/15 11:36:58</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/17 10:03:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11476.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/17 11:34:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11476</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/17 10:03:34</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11476.71</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 10:03:28</t>
+          <t>09/23 15:27:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>17261.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/17 11:34:30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 10:03:34</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>145000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17261.9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>17261.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/23 15:27:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>145000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17261.9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17261.9</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17073.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/23 17:00:58</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17073</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/23 15:27:50</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>145000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>17261.9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17073.9</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 15:27:39</t>
+          <t>09/24 10:57:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 17:00:58</t>
+          <t>09/24 10:57:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -217,7 +217,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -226,86 +226,59 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>09/23 15:27:50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17261.9</t>
+          <t>388</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17261</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.9</t>
+          <t>5494.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/24 12:28:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5494</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/24 10:57:06</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5494.35</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 10:57:00</t>
+          <t>09/29 20:58:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>18823.53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/24 12:28:36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5494</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 10:57:06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18823.53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5882.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>18823.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/29 21:09:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18823.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18823.53</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18635.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 20:58:34</t>
+          <t>10/01 14:45:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/29 21:09:02</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18823.53</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>18635.53</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/01 15:51:12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12048.19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12048.19</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.19</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 14:45:35</t>
+          <t>10/11 10:01:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/01 15:51:12</t>
+          <t>10/11 10:01:38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>5594.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/11 13:28:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5594</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/11 10:01:38</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>5882.35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5594.35</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.35</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/11 10:01:32</t>
+          <t>10/13 12:17:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5882.35</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/11 13:28:54</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5594</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/11 10:01:38</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5882.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5882</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.35</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/13 13:53:32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 12:17:55</t>
+          <t>10/16 13:26:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>17365.27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/13 13:53:32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>17365.27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>17365.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/16 15:30:26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17365</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>145000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17365.27</t>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17365.27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17365</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17365.27</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 13:26:03</t>
+          <t>10/26 10:21:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17365.27</t>
+          <t>26506.02</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/16 15:30:26</t>
+          <t>10/26 11:45:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -217,7 +217,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>220000</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17365.27</t>
+          <t>26506.02</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>26506</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 10:21:47</t>
+          <t>10/30 20:12:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26506.02</t>
+          <t>13095.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/26 11:45:40</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>26506</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>13095.24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26506.02</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26506</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.02</t>
+          <t>13095.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/30 21:49:04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13095</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13095.24</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13095.24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13095</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13095.24</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.24</t>
         </is>
       </c>
     </row>
